--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487648_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487648_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0728</v>
+        <v>2.9283</v>
       </c>
       <c r="E2" t="n">
-        <v>5.913</v>
+        <v>3.932</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-1.0037</v>
       </c>
       <c r="G2" t="n">
         <v>2.0922</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0747</v>
+        <v>-0.0698</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2166</v>
+        <v>1.2357</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1419</v>
+        <v>-1.3055</v>
       </c>
       <c r="V2" t="n">
         <v>2.0701</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0468</v>
+        <v>2.3254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8605</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1863</v>
+        <v>1.8047</v>
       </c>
       <c r="G3" t="n">
         <v>1.1701</v>
@@ -688,13 +688,13 @@
         <v>0.5821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5689</v>
+        <v>-0.1525</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3768</v>
+        <v>0.037</v>
       </c>
       <c r="U3" t="n">
-        <v>0.192</v>
+        <v>-0.1895</v>
       </c>
       <c r="V3" t="n">
         <v>0.7257</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3969</v>
+        <v>1.5818</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1753</v>
+        <v>3.0663</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7783</v>
+        <v>-1.4845</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9481</v>
+        <v>-0.3933</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.4443</v>
+        <v>0.6039</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3924</v>
+        <v>-0.9971</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2408</v>
+        <v>2.117</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4408</v>
+        <v>0.795</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6816</v>
+        <v>1.3219</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2927</v>
+        <v>-2.5102</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0035</v>
+        <v>-0.1912</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2892</v>
+        <v>-2.3191</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5512</v>
+        <v>0.2571</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6808</v>
+        <v>0.6956</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2319</v>
+        <v>-0.4385</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9418</v>
       </c>
       <c r="W4" t="n">
         <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2267</v>
+        <v>1.2718</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3841</v>
+        <v>3.6958</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1574</v>
+        <v>-2.424</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3933</v>
+        <v>1.9481</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6039</v>
+        <v>-1.4443</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9971</v>
+        <v>3.3924</v>
       </c>
       <c r="J5" t="n">
-        <v>2.117</v>
+        <v>3.2408</v>
       </c>
       <c r="K5" t="n">
-        <v>0.795</v>
+        <v>-0.4408</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3219</v>
+        <v>3.6816</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5102</v>
+        <v>-1.2927</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1912</v>
+        <v>-1.0035</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3191</v>
+        <v>-0.2892</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.098</v>
+        <v>-0.6763</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0134</v>
+        <v>0.2013</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1114</v>
+        <v>-0.8776</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5773</v>
+        <v>1.0199</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0446</v>
+        <v>4.4054</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.4673</v>
+        <v>-3.3855</v>
       </c>
       <c r="G6" t="n">
         <v>1.5516</v>
@@ -922,13 +922,13 @@
         <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.2626</v>
+        <v>-1.82</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6539</v>
+        <v>-0.293</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6087</v>
+        <v>-1.527</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2639</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.239</v>
+        <v>0.2859</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2624</v>
+        <v>0.3987</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0234</v>
+        <v>-0.1129</v>
       </c>
       <c r="G7" t="n">
         <v>0.9792999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.79</v>
+        <v>-1.2651</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9691</v>
+        <v>-0.3079</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8209</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0.3776</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1975</v>
+        <v>-2.2192</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1873</v>
+        <v>-0.0524</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3848</v>
+        <v>-2.1668</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4694</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9583</v>
+        <v>-0.98</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6684</v>
+        <v>0.4287</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6267</v>
+        <v>-1.4087</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1579</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.2724</v>
+        <v>-3.8594</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.2937</v>
+        <v>-5.0715</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0214</v>
+        <v>1.2122</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9278999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.5298</v>
+        <v>-1.1168</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0902</v>
+        <v>0.132</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4396</v>
+        <v>-1.2488</v>
       </c>
       <c r="V9" t="n">
         <v>1.2898</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.5894</v>
+        <v>-5.4038</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0714</v>
+        <v>-2.0494</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5179</v>
+        <v>-3.3544</v>
       </c>
       <c r="G10" t="n">
         <v>-7.0323</v>
@@ -1234,13 +1234,13 @@
         <v>1.7463</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1588</v>
+        <v>-0.9732</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8356</v>
+        <v>0.1864</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3232</v>
+        <v>-1.1597</v>
       </c>
       <c r="V10" t="n">
         <v>2.7958</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9778</v>
+        <v>-2.0693</v>
       </c>
       <c r="E11" t="n">
-        <v>7.937299999999999</v>
+        <v>8.845599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.9148</v>
+        <v>-10.9149</v>
       </c>
       <c r="G11" t="n">
         <v>-1.081600000000001</v>
@@ -1312,13 +1312,13 @@
         <v>12.6122</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.705099999999998</v>
+        <v>-6.7966</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4072</v>
+        <v>2.3158</v>
       </c>
       <c r="U11" t="n">
-        <v>-9.112299999999999</v>
+        <v>-9.112500000000001</v>
       </c>
       <c r="V11" t="n">
         <v>6.779</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.153</v>
+        <v>3.9072</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0002</v>
+        <v>4.6999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8472</v>
+        <v>-0.7927</v>
       </c>
       <c r="G12" t="n">
         <v>3.2553</v>
@@ -1390,13 +1390,13 @@
         <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.6519</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0924</v>
+        <v>0.7921</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1947</v>
+        <v>-0.1402</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1497</v>
+        <v>3.0028</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6255</v>
+        <v>2.9001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5242</v>
+        <v>0.1027</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.278</v>
+        <v>3.9847</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.4871</v>
+        <v>1.1963</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2091</v>
+        <v>2.7884</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2493</v>
+        <v>5.6893</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3305</v>
+        <v>2.6117</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08119999999999999</v>
+        <v>3.0776</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0286</v>
+        <v>-1.7046</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1565</v>
+        <v>-1.4154</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1279</v>
+        <v>-0.2892</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5821</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5821</v>
+        <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2259</v>
+        <v>1.0226</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6509</v>
+        <v>1.1392</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5749</v>
+        <v>-0.1166</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6197</v>
+        <v>-0.4522</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2239</v>
+        <v>-0.0478</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3958</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9149</v>
+        <v>2.5033</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0002</v>
+        <v>3.7434</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0853</v>
+        <v>-1.2401</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9847</v>
+        <v>0.4531</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1963</v>
+        <v>-1.5011</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7884</v>
+        <v>1.9542</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6893</v>
+        <v>2.3637</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6117</v>
+        <v>-0.2801</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0776</v>
+        <v>2.6438</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7046</v>
+        <v>-1.9106</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4154</v>
+        <v>-1.221</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2892</v>
+        <v>-0.6896</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5523</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9347</v>
+        <v>0.4887</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2393</v>
+        <v>0.8723</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3046</v>
+        <v>-0.3835</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4522</v>
+        <v>1.9496</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0478</v>
+        <v>2.4477</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4045</v>
+        <v>-0.4982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6991</v>
+        <v>2.4584</v>
       </c>
       <c r="E15" t="n">
-        <v>3.773</v>
+        <v>1.125</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0738</v>
+        <v>1.3334</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4412</v>
+        <v>-1.278</v>
       </c>
       <c r="H15" t="n">
-        <v>0.968</v>
+        <v>-1.4871</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4732</v>
+        <v>0.2091</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2882</v>
+        <v>-1.2493</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9485</v>
+        <v>-1.3305</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3397</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8469</v>
+        <v>-0.0286</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9804</v>
+        <v>-0.1565</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1335</v>
+        <v>0.1279</v>
       </c>
       <c r="P15" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.9702</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2561</v>
+        <v>1.5346</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8326</v>
+        <v>1.1504</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5765</v>
+        <v>0.3842</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9982</v>
+        <v>1.6197</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3776</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6206</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2143</v>
+        <v>2.1347</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6423</v>
+        <v>3.0723</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4281</v>
+        <v>-0.9376</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4531</v>
+        <v>2.4412</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.5011</v>
+        <v>0.968</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9542</v>
+        <v>1.4732</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3637</v>
+        <v>3.2882</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2801</v>
+        <v>1.9485</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6438</v>
+        <v>1.3397</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9106</v>
+        <v>-0.8469</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.221</v>
+        <v>-0.9804</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6896</v>
+        <v>0.1335</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8004</v>
+        <v>0.6917</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2288</v>
+        <v>1.1319</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5715</v>
+        <v>-0.4402</v>
       </c>
       <c r="V16" t="n">
-        <v>1.9496</v>
+        <v>-0.9982</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>-0.3776</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4982</v>
+        <v>-0.6206</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9872</v>
+        <v>1.5578</v>
       </c>
       <c r="E17" t="n">
-        <v>0.249</v>
+        <v>0.8496</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7383</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.9433</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4484</v>
+        <v>1.0189</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0987</v>
+        <v>0.6993</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3497</v>
+        <v>0.3197</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0164</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1603</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9169</v>
+        <v>0.8168</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7567</v>
+        <v>-0.7294</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7922</v>
@@ -1858,13 +1858,13 @@
         <v>0.3881</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5644</v>
+        <v>0.4915</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5462</v>
+        <v>0.4461</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0772</v>
+        <v>-0.5406</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2258</v>
+        <v>-0.8254</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1486</v>
+        <v>0.2848</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9147999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0179</v>
+        <v>0.5187</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3286</v>
+        <v>0.729</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3465</v>
+        <v>-0.2103</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3385</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0967</v>
+        <v>-2.0633</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2833</v>
+        <v>-0.3834</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8134</v>
+        <v>-1.6799</v>
       </c>
       <c r="G20" t="n">
         <v>1.4722</v>
@@ -2014,13 +2014,13 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1063</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3163</v>
+        <v>0.2162</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2434</v>
+        <v>-0.1099</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0597</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1778</v>
+        <v>-2.3203</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9051</v>
+        <v>-2.5196</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0829</v>
+        <v>0.1993</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6556</v>
+        <v>-3.1162</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8092</v>
+        <v>-2.797</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8464</v>
+        <v>-0.3192</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0152</v>
+        <v>-2.563</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6344</v>
+        <v>-2.1214</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6495</v>
+        <v>-0.4415</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6708</v>
+        <v>-0.5533</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1748</v>
+        <v>-0.6756</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.496</v>
+        <v>0.1223</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8077</v>
+        <v>1.3195</v>
       </c>
       <c r="T21" t="n">
-        <v>1.578</v>
+        <v>1.0329</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2297</v>
+        <v>0.2866</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9418</v>
+        <v>-2.2699</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>-0.9896</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-1.2803</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>D. GONZALEZ  LONGARELA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1896</v>
+        <v>-3.1421</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1192</v>
+        <v>0.1043</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0704</v>
+        <v>-3.2464</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1162</v>
+        <v>-2.6556</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.797</v>
+        <v>-1.8092</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3192</v>
+        <v>-0.8464</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.563</v>
+        <v>0.0152</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1214</v>
+        <v>-0.6344</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4415</v>
+        <v>0.6495</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5533</v>
+        <v>-2.6708</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6756</v>
+        <v>-1.1748</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1223</v>
+        <v>-1.496</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7463</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4502</v>
+        <v>0.8434</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4333</v>
+        <v>0.7772</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0168</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.2699</v>
+        <v>-0.9418</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.9896</v>
+        <v>0.2821</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2803</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7594</v>
+        <v>-3.9403</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2869</v>
+        <v>-2.386</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4725</v>
+        <v>-1.5542</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7114</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1346</v>
+        <v>-0.3154</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.775</v>
+        <v>0.1259</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3595</v>
+        <v>-0.4413</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2716</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.977799999999998</v>
+        <v>3.645000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>11.197</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.219199999999999</v>
+        <v>-7.5519</v>
       </c>
       <c r="G24" t="n">
-        <v>1.081600000000002</v>
+        <v>1.081600000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-7.0935</v>
       </c>
       <c r="I24" t="n">
-        <v>8.1751</v>
+        <v>8.175099999999999</v>
       </c>
       <c r="J24" t="n">
         <v>12.8653</v>
       </c>
       <c r="K24" t="n">
-        <v>1.186700000000001</v>
+        <v>1.1867</v>
       </c>
       <c r="L24" t="n">
         <v>11.6788</v>
@@ -2314,10 +2314,10 @@
         <v>-8.280000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.5037</v>
+        <v>-3.503699999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.97</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.6121</v>
@@ -2326,16 +2326,16 @@
         <v>13.5824</v>
       </c>
       <c r="S24" t="n">
-        <v>7.705100000000001</v>
+        <v>8.372399999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>9.112499999999999</v>
+        <v>9.112500000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4074</v>
+        <v>-0.7399</v>
       </c>
       <c r="V24" t="n">
-        <v>-6.779</v>
+        <v>-6.778999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>1.8312</v>
